--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1048,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123204693</v>
+        <v>137013866</v>
       </c>
       <c r="B5" t="n">
-        <v>97983</v>
+        <v>92524</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,49 +1059,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>5420</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mellansjön, Sm</t>
+          <t>Obyskogen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468906</v>
+        <v>468914</v>
       </c>
       <c r="R5" t="n">
-        <v>6295262</v>
+        <v>6295349</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1125,12 +1124,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>årets</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,6 +1152,11 @@
           <t>barrskog</t>
         </is>
       </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
@@ -1162,16 +1171,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123204693</t>
+          <t>https://artportalen.se/Sighting/137013866</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122607861</v>
+        <v>123204693</v>
       </c>
       <c r="B6" t="n">
-        <v>97985</v>
+        <v>97983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,22 +1188,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224363</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1207,17 +1220,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Avd 55, Mellansjön, Sm</t>
+          <t>Mellansjön, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468898</v>
+        <v>468906</v>
       </c>
       <c r="R6" t="n">
-        <v>6295261</v>
+        <v>6295262</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1241,12 +1254,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,27 +1268,143 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Grova barrträd med torrakor och lågor, fuktig mark intill maden.</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Caroline Mortlock</t>
+          <t>Per Darell</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Caroline Mortlock, Per Darell</t>
+          <t>Per Darell</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123204693</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122607861</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Avd 55, Mellansjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>468898</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6295261</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Blädinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-02-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Grova barrträd med torrakor och lågor, fuktig mark intill maden.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Caroline Mortlock</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Caroline Mortlock, Per Darell</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/122607861</t>
         </is>
@@ -1288,6 +1417,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>137013866</v>
       </c>
       <c r="B5" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>137013866</v>
       </c>
       <c r="B5" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>137013866</v>
       </c>
       <c r="B5" t="n">
-        <v>92528</v>
+        <v>92529</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>137013866</v>
       </c>
       <c r="B5" t="n">
-        <v>92529</v>
+        <v>92535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>137013866</v>
       </c>
       <c r="B5" t="n">
-        <v>92535</v>
+        <v>92539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>137013866</v>
       </c>
       <c r="B5" t="n">
-        <v>92539</v>
+        <v>92541</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>137013866</v>
       </c>
       <c r="B5" t="n">
-        <v>92541</v>
+        <v>92554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>137013866</v>
       </c>
       <c r="B5" t="n">
-        <v>92554</v>
+        <v>92556</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>137013866</v>
       </c>
       <c r="B5" t="n">
-        <v>92556</v>
+        <v>92559</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>137013866</v>
       </c>
       <c r="B5" t="n">
-        <v>92559</v>
+        <v>92569</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>137013866</v>
       </c>
       <c r="B5" t="n">
-        <v>92569</v>
+        <v>92570</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>137013866</v>
       </c>
       <c r="B5" t="n">
-        <v>92570</v>
+        <v>92573</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>137013866</v>
       </c>
       <c r="B5" t="n">
-        <v>92573</v>
+        <v>92575</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>137013866</v>
       </c>
       <c r="B5" t="n">
-        <v>92575</v>
+        <v>92580</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>137013866</v>
       </c>
       <c r="B5" t="n">
-        <v>92580</v>
+        <v>92592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>137013866</v>
       </c>
       <c r="B5" t="n">
-        <v>92592</v>
+        <v>92593</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>137013866</v>
       </c>
       <c r="B5" t="n">
-        <v>92593</v>
+        <v>92596</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>137013866</v>
       </c>
       <c r="B5" t="n">
-        <v>92596</v>
+        <v>92597</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52675-2024 artfynd.xlsx
+++ b/artfynd/A 52675-2024 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>137013866</v>
       </c>
       <c r="B5" t="n">
-        <v>92597</v>
+        <v>92600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
